--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 08:23</v>
+        <v>01/11/2026 08:37</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 08:37</v>
+        <v>01/11/2026 08:44</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 08:44</v>
+        <v>01/11/2026 08:51</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 08:51</v>
+        <v>01/11/2026 08:56</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 08:56</v>
+        <v>01/11/2026 09:01</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 09:01</v>
+        <v>01/11/2026 09:06</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 09:06</v>
+        <v>01/11/2026 12:28</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 12:28</v>
+        <v>01/11/2026 12:49</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 12:49</v>
+        <v>01/11/2026 13:00</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 13:00</v>
+        <v>01/11/2026 13:10</v>
       </c>
     </row>
   </sheetData>

--- a/tests/moto/resultats/carnet-e2e.xlsx
+++ b/tests/moto/resultats/carnet-e2e.xlsx
@@ -469,7 +469,7 @@
         <v>Exporté le</v>
       </c>
       <c r="B9" t="str">
-        <v>01/11/2026 13:10</v>
+        <v>01/11/2026 13:16</v>
       </c>
     </row>
   </sheetData>
